--- a/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,7</t>
+          <t>-1,2; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,0</t>
+          <t>-3,34; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,44</t>
+          <t>-0,62; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,12</t>
+          <t>-0,66; 2,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>-2,22; 0,0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>-1,96; 0,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 0,0</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,96; —</t>
+          <t>-87,72; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,41</t>
+          <t>-2,42; 0,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,18</t>
+          <t>-1,96; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,21</t>
+          <t>-3,08; -0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,28</t>
+          <t>-0,98; 1,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,72</t>
+          <t>-1,35; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,7</t>
+          <t>-1,05; 1,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,48</t>
+          <t>-1,38; 0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,62</t>
+          <t>-1,38; 0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,36</t>
+          <t>-1,34; 0,44</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 195,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 179,81</t>
+          <t>-88,02; 162,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,25</t>
+          <t>-100,0; 246,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,76</t>
+          <t>-1,26; 4,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,81</t>
+          <t>-2,44; 2,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,47</t>
+          <t>-3,77; 0,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,67</t>
+          <t>-2,02; 2,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,19</t>
+          <t>-2,25; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,88</t>
+          <t>-3,15; 0,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,12</t>
+          <t>-0,96; 3,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,98</t>
+          <t>-1,55; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,27</t>
+          <t>-2,49; 0,39</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,44; —</t>
+          <t>-56,74; 879,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,79; 485,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 436,99</t>
+          <t>-43,36; 397,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 281,91</t>
+          <t>-64,65; 390,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,09</t>
+          <t>-100,0; 186,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,4</t>
+          <t>-0,11; 5,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,84</t>
+          <t>-2,72; 0,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,38</t>
+          <t>-1,07; 3,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,94</t>
+          <t>-1,88; 3,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,36</t>
+          <t>-2,69; 2,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,25</t>
+          <t>-3,04; 0,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,1</t>
+          <t>-0,44; 3,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,12</t>
+          <t>-2,08; 0,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,79</t>
+          <t>-1,37; 1,81</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 736,08</t>
+          <t>-30,94; 813,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 349,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 539,75</t>
+          <t>-45,4; 528,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 323,35</t>
+          <t>-62,37; 317,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,75; 225,71</t>
+          <t>-85,64; 187,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,89; 138,66</t>
+          <t>-87,1; 112,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 320,73</t>
+          <t>-28,48; 264,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 94,23</t>
+          <t>-76,06; 90,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 138,86</t>
+          <t>-51,92; 141,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,88</t>
+          <t>-0,42; 1,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,61</t>
+          <t>-1,27; 0,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,27</t>
+          <t>-0,86; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,52</t>
+          <t>-0,49; 1,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,65</t>
+          <t>-1,16; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,65</t>
+          <t>-1,16; 0,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,36</t>
+          <t>-0,17; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,42</t>
+          <t>-0,95; 0,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,58</t>
+          <t>-0,76; 0,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 223,74</t>
+          <t>-24,75; 230,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 81,44</t>
+          <t>-67,71; 78,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 145,41</t>
+          <t>-49,61; 169,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 189,97</t>
+          <t>-35,59; 211,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,58; 98,17</t>
+          <t>-71,45; 85,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 90,76</t>
+          <t>-69,3; 100,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 142,12</t>
+          <t>-12,79; 145,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 48,87</t>
+          <t>-58,49; 31,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 62,43</t>
+          <t>-47,76; 65,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,65</t>
+          <t>-1,73; 2,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,0</t>
+          <t>-2,89; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,24</t>
+          <t>-1,06; 3,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,67; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,23</t>
+          <t>-0,59; 2,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,0</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,72; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,32</t>
+          <t>-2,68; 0,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,23</t>
+          <t>-2,03; 1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -0,29</t>
+          <t>-2,89; -0,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,3</t>
+          <t>-0,81; 1,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,62</t>
+          <t>-1,32; 0,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,5</t>
+          <t>-0,83; 1,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,49</t>
+          <t>-1,41; 0,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,55</t>
+          <t>-1,22; 0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,44</t>
+          <t>-1,47; 0,36</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,43</t>
+          <t>-100,0; 176,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 162,94</t>
+          <t>-89,23; 177,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,37</t>
+          <t>-100,0; 157,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,6</t>
+          <t>-1,06; 4,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,8</t>
+          <t>-2,17; 2,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,46</t>
+          <t>-4,12; 0,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,63</t>
+          <t>-2,09; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,13</t>
+          <t>-2,43; 2,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,73</t>
+          <t>-3,14; 0,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,03</t>
+          <t>-0,98; 2,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,06</t>
+          <t>-1,62; 1,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,39</t>
+          <t>-2,59; 0,36</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 879,26</t>
+          <t>-57,76; 885,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 485,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 397,65</t>
+          <t>-46,6; 403,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 390,96</t>
+          <t>-66,63; 271,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,43</t>
+          <t>-100,0; 113,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 5,85</t>
+          <t>-0,56; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,87</t>
+          <t>-2,84; 0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,99</t>
+          <t>-0,99; 4,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,75</t>
+          <t>-1,93; 3,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,35</t>
+          <t>-2,66; 2,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,99</t>
+          <t>-3,21; 1,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,45</t>
+          <t>-0,29; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,92</t>
+          <t>-2,08; 0,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,81</t>
+          <t>-1,28; 1,95</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 813,04</t>
+          <t>-35,36; 749,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 528,42</t>
+          <t>-44,91; 613,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 317,28</t>
+          <t>-59,76; 323,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 187,96</t>
+          <t>-78,19; 234,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 112,86</t>
+          <t>-85,13; 133,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 264,46</t>
+          <t>-16,65; 307,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,06; 90,63</t>
+          <t>-75,73; 79,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 141,24</t>
+          <t>-47,43; 167,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,95</t>
+          <t>-0,46; 1,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,61</t>
+          <t>-1,31; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,44</t>
+          <t>-1,04; 1,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,54</t>
+          <t>-0,57; 1,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,61</t>
+          <t>-1,17; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,67</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,36</t>
+          <t>-0,25; 1,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,29</t>
+          <t>-0,87; 0,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,65</t>
+          <t>-0,8; 0,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 230,13</t>
+          <t>-24,71; 241,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 78,22</t>
+          <t>-68,68; 70,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 169,36</t>
+          <t>-59,15; 185,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 211,18</t>
+          <t>-33,66; 181,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 85,67</t>
+          <t>-66,43; 103,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 100,05</t>
+          <t>-69,64; 104,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 145,75</t>
+          <t>-15,53; 141,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 31,81</t>
+          <t>-53,93; 48,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 65,16</t>
+          <t>-50,51; 67,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,22</t>
+          <t>-0,58; 3,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,0</t>
+          <t>-2,69; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-2,69; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,15</t>
+          <t>-1,19; 2,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-2,91; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,29</t>
+          <t>-0,62; 2,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,0</t>
+          <t>-1,96; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>185,4%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>90,06%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>185,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,96; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,28</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,36</t>
+          <t>-0,85; 1,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,25</t>
+          <t>-1,13; 0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,21</t>
+          <t>-0,85; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,45</t>
+          <t>-2,32; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,88</t>
+          <t>-2,0; 1,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,89</t>
+          <t>-2,42; 0,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,54</t>
+          <t>-1,35; 0,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,26; 0,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,36</t>
+          <t>-1,27; 0,49</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-45,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-70,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-22,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-91,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-45,21%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>-71,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,74%</t>
+          <t>-39,26%</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 176,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,23; 177,58</t>
+          <t>-86,99; 179,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,55</t>
+          <t>-100,0; 181,52</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,71</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,44</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,82</t>
+          <t>-2,09; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,96</t>
+          <t>-2,35; 2,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,47</t>
+          <t>-3,12; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,65</t>
+          <t>-1,16; 4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,19</t>
+          <t>-2,46; 2,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,81</t>
+          <t>-3,78; 0,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,92</t>
+          <t>-0,74; 3,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,84</t>
+          <t>-1,36; 1,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,36</t>
+          <t>-2,58; 0,25</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-47,77%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>103,44%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>27,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-70,43%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,22%</t>
+          <t>-74,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-59,67%</t>
+          <t>-60,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,76; 885,18</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-64,44; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 403,0</t>
+          <t>-44,8; 436,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,63; 271,83</t>
+          <t>-60,94; 281,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,13</t>
+          <t>-100,0; 116,05</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,5</t>
+          <t>-1,56; 3,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,86</t>
+          <t>-2,65; 2,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,12</t>
+          <t>-3,03; 1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,65</t>
+          <t>-0,54; 5,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,25</t>
+          <t>-2,71; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,08</t>
+          <t>-0,46; 4,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,78</t>
+          <t>-0,29; 4,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,98</t>
+          <t>-2,02; 1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,95</t>
+          <t>-1,33; 2,1</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-7,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-34,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>131,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-53,74%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>86,68%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-7,76%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-34,47%</t>
+          <t>111,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 749,35</t>
+          <t>-50,86; 323,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,75; 225,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 613,3</t>
+          <t>-84,55; 139,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 323,67</t>
+          <t>-32,29; 736,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 234,34</t>
+          <t>-100,0; 349,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 133,8</t>
+          <t>-33,48; 640,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 307,25</t>
+          <t>-21,3; 320,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 79,63</t>
+          <t>-75,25; 94,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 167,5</t>
+          <t>-49,37; 160,39</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,8</t>
+          <t>-0,58; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,57</t>
+          <t>-1,17; 0,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,35</t>
+          <t>-1,08; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,45</t>
+          <t>-0,39; 1,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,72</t>
+          <t>-1,28; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-0,79; 1,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,35</t>
+          <t>-0,16; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,41</t>
+          <t>-0,86; 0,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,65</t>
+          <t>-0,71; 0,75</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-18,07%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>53,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-18,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,05%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 241,5</t>
+          <t>-37,97; 189,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 70,9</t>
+          <t>-65,58; 98,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 185,97</t>
+          <t>-65,21; 103,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 181,56</t>
+          <t>-28,36; 223,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 103,37</t>
+          <t>-70,93; 81,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 104,99</t>
+          <t>-48,76; 184,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 141,25</t>
+          <t>-12,35; 142,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 48,68</t>
+          <t>-56,02; 48,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 67,59</t>
+          <t>-45,56; 78,14</t>
         </is>
       </c>
     </row>
